--- a/experiment_results.xlsx
+++ b/experiment_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4180,6 +4180,1586 @@
         <v>93.59999999999999</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2025-12-10 11:32:48</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_111103</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_111103/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_111103/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="H94" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="I94" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="J94" t="n">
+        <v>92.09999999999999</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025-12-10 11:33:26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_113323</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_113323/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_113323/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025-12-10 11:57:22</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_113538</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_113538/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_113538/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="H96" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="I96" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="J96" t="n">
+        <v>91.40000000000001</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2025-12-10 12:26:48</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_120514</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_120514/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_120514/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="I97" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="J97" t="n">
+        <v>88.90000000000001</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025-12-10 13:20:54</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_125925</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_125925/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_125925/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>75</v>
+      </c>
+      <c r="H98" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="I98" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="J98" t="n">
+        <v>90.90000000000001</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025-12-10 13:49:27</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_132803</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_132803/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_132803/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="H99" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="I99" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J99" t="n">
+        <v>92.7</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-12-10 14:20:15</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_135845</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_135845/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_135845/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="H100" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="J100" t="n">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-12-10 14:53:21</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_143149</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_143149/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_143149/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="H101" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="I101" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="J101" t="n">
+        <v>90.09999999999999</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-12-10 15:19:18</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_145748</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_145748/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_145748/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="H102" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="I102" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="J102" t="n">
+        <v>90.90000000000001</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-12-10 16:50:58</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_164308</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_164308/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_164308/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="I103" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="J103" t="n">
+        <v>89.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-12-10 17:12:35</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_165127</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_165127/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_165127/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="H104" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="I104" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="J104" t="n">
+        <v>89.59999999999999</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-12-10 17:46:21</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_172409</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_172409/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_172409/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="H105" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="I105" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="J105" t="n">
+        <v>88.59999999999999</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-12-10 18:24:57</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_180246</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_180246/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_180246/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="H106" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="I106" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="J106" t="n">
+        <v>87.59999999999999</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-12-10 18:58:59</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_183650</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_183650/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_183650/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="H107" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="I107" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="J107" t="n">
+        <v>92.09999999999999</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-12-10 19:33:32</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_191126</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_191126/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_191126/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="H108" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I108" t="n">
+        <v>90</v>
+      </c>
+      <c r="J108" t="n">
+        <v>92.09999999999999</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-12-10 20:27:03</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_202658</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_202658/configs/experiment_config.yml MODEL.USE_MULTI_SCALE True MODEL.USE_MULTI_SCALE_MOE True MODEL.MOE_USE_FIXED_WEIGHTS True MODEL.MOE_FIXED_WEIGHTS [0.33,0.33,0.34] MODEL.USE_GATE_FUSION False MODEL.USE_ATTENTION_FUSION False MODEL.MOE_BALANCE_LOSS_WEIGHT 0.0 MODEL.MOE_SPARSITY_LOSS_WEIGHT 0.0 MODEL.MOE_DIVERSITY_LOSS_WEIGHT 0.0 SOLVER.MOE_BALANCE_LOSS_WEIGHT 0.0 SOLVER.MOE_SPARSITY_LOSS_WEIGHT 0.0 SOLVER.MOE_DIVERSITY_LOSS_WEIGHT 0.0 SOLVER.MOE_USE_DYNAMIC_LOSS_WEIGHT False SOLVER.MOE_BALANCE_LOSS_WEIGHT_START 0.0 SOLVER.MOE_BALANCE_LOSS_WEIGHT_END 0.0 SOLVER.MOE_DIVERSITY_LOSS_WEIGHT_START 0.0 SOLVER.MOE_DIVERSITY_LOSS_WEIGHT_END 0.0 OUTPUT_DIR ./outputs/V8.0_Fixed_Weights_Clean 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_202658/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>4, 8, 16</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-12-10 21:14:26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_205215</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_205215/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_205215/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="H110" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="I110" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J110" t="n">
+        <v>92.7</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-12-10 21:39:03</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_211653</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_211653/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_211653/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>简单拼接</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="H111" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="I111" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J111" t="n">
+        <v>91.90000000000001</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-12-10 22:12:03</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_214956</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_214956/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_214956/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>75</v>
+      </c>
+      <c r="H112" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="I112" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="J112" t="n">
+        <v>89.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-12-10 22:35:13</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_221305</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_221305/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_221305/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="H113" t="n">
+        <v>81</v>
+      </c>
+      <c r="I113" t="n">
+        <v>88</v>
+      </c>
+      <c r="J113" t="n">
+        <v>92.5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-12-10 23:01:30</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_223919</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_223919/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_223919/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>4, 8, 16</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="H114" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="I114" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="J114" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-12-10 23:26:44</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_230431</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_230431/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_230431/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="H115" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="I115" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="J115" t="n">
+        <v>91.3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-12-10 23:49:39</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251210_232725</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251210_232725/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251210_232725/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="I116" t="n">
+        <v>88</v>
+      </c>
+      <c r="J116" t="n">
+        <v>91.3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:43:50</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_002143</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_002143/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_002143/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="H117" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="I117" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="J117" t="n">
+        <v>88.40000000000001</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:44:27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_004424</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_004424/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_004424/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:45:11</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_004509</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_004509/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_004509/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-12-11 01:22:27</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_005957</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_005957/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_005957/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="J120" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-12-11 01:48:46</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_012637</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_012637/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_012637/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="H121" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="I121" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="J121" t="n">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-12-11 03:12:16</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_025001</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_025001/configs/experiment_config.yml MODEL.MOE_USE_TOP_K_ROUTING True MODEL.MOE_TOP_K 2 MODEL.MOE_TOP_K_MODE soft SOLVER.MOE_BALANCE_LOSS_WEIGHT 0.0010 SOLVER.MOE_DIVERSITY_LOSS_WEIGHT 0.0010 OUTPUT_DIR ./outputs/V24.1_Top2_Soft_Minimal 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_025001/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>4, 8, 16</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="I122" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-12-11 03:37:25</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_031511</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_031511/configs/experiment_config.yml MODEL.MOE_USE_TOP_K_ROUTING False SOLVER.MOE_BALANCE_LOSS_WEIGHT 0.0100 SOLVER.MOE_DIVERSITY_LOSS_WEIGHT 0.0010 OUTPUT_DIR ./outputs/V23.1_Balance_x10 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_031511/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>4, 8, 16</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="H123" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="I123" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="J123" t="n">
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-12-11 04:54:44</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_043227</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_043227/configs/experiment_config.yml MODEL.MOE_USE_TOP_K_ROUTING True MODEL.MOE_TOP_K 2 MODEL.MOE_TOP_K_MODE soft SOLVER.MOE_BALANCE_LOSS_WEIGHT 0.0010 SOLVER.MOE_DIVERSITY_LOSS_WEIGHT 0.0010 OUTPUT_DIR ./outputs/V25.1_Top2_YAML_Lock 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_043227/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>4, 8, 16</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="I124" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="J124" t="n">
+        <v>87.90000000000001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-12-11 14:49:02</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_142752</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_142752/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_142752/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="I125" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="J125" t="n">
+        <v>92.2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-12-11 15:51:06</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_152958</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_152958/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_152958/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="H126" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-12-11 16:16:10</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_155504</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_155504/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_155504/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="H127" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="I127" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J127" t="n">
+        <v>91.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-12-11 17:04:17</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_164214</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_164214/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_164214/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="H128" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="I128" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="J128" t="n">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-12-11 17:32:43</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_171028</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_171028/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_171028/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H129" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="I129" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="J129" t="n">
+        <v>92.59999999999999</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-12-11 17:55:39</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_173329</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_173329/configs/experiment_config.yml 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_173329/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>77</v>
+      </c>
+      <c r="H130" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="I130" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="J130" t="n">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-12-11 19:26:52</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_190435</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_190435/configs/experiment_config.yml SOLVER.MOE_BALANCE_LOSS_WEIGHT 0.0005 SOLVER.MOE_DIVERSITY_LOSS_WEIGHT 0.0005 SOLVER.MOE_SPARSITY_LOSS_WEIGHT 0.0001 SOLVER.MOE_USE_DYNAMIC_LOSS_WEIGHT True SOLVER.MOE_LOSS_WEIGHT_WARMUP_EPOCHS 10 SOLVER.MOE_LOSS_WEIGHT_SCHEDULE_TYPE cosine SOLVER.MOE_BALANCE_LOSS_WEIGHT_START 0.0002 SOLVER.MOE_BALANCE_LOSS_WEIGHT_END 0.0025 SOLVER.MOE_DIVERSITY_LOSS_WEIGHT_START 0.0002 SOLVER.MOE_DIVERSITY_LOSS_WEIGHT_END 0.002 MODEL.MOE_TEMPERATURE 0.55 MODEL.GATE_DROPOUT 0.2 MODEL.MOE_USE_TOP_K_ROUTING True MODEL.MOE_TOP_K 2 MODEL.MOE_TOP_K_MODE soft 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_190435/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="H131" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="I131" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="J131" t="n">
+        <v>91.40000000000001</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-12-11 19:50:50</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>RGBNT201</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>results/everyExperiments/experiment_20251211_195047</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>python train_net.py --config_file results/everyExperiments/experiment_20251211_195047/configs/experiment_config.yml MODEL.USE_GATE_FUSION False MODEL.USE_ATTENTION_FUSION False MODEL.MOE_USE_TOP_K_ROUTING False MODEL.MOE_USE_FIXED_WEIGHTS False MODEL.WAVELET_ENABLE False MODEL.WAVELET_GATE_ENABLE False MODEL.WAVELET_SCALE_ENABLE False OUTPUT_DIR ./outputs/replay_soft_moe_20251013 2&gt;&amp;1 | tee results/everyExperiments/experiment_20251211_195047/logs/train_log.txt</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>无预处理</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
